--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5275,8 +5405,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -5299,1305 +5433,1401 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야월삼경 — 민요채보-2/야월삼경.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">야월삼경</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">온</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="19"/>
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">한</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="19"/>
+      <c r="N4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="O4" s="19"/>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="19"/>
+      <c r="T4" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="U4" s="19"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="C5" s="20"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E5" s="20"/>
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="G5" s="20"/>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="20"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="20"/>
+      <c r="L5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="20"/>
+      <c r="N5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S5" s="20"/>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U5" s="20"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G6" s="18"/>
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="18"/>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="18"/>
+      <c r="L6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="18"/>
+      <c r="P6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="Q6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">회</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="L7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="19"/>
+      <c r="N7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="19"/>
+      <c r="T7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="20"/>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="20"/>
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="20"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="L8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="Q8" s="20"/>
+      <c r="R8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S8" s="20"/>
+      <c r="T8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="U8" s="20"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I9" s="18"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">식</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="Q9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="S9" s="18"/>
+      <c r="T9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M10" s="19"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O10" s="19"/>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S10" s="19"/>
+      <c r="T10" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="E11" s="20"/>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="20"/>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="20"/>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="20"/>
+      <c r="P11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="20"/>
+      <c r="R11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="S11" s="20"/>
+      <c r="T11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="U11" s="20"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="18"/>
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="G12" s="18"/>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="18"/>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="18"/>
+      <c r="P12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="Q12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="T12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="19"/>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="K13" s="19"/>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="O13" s="19"/>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S13" s="19"/>
+      <c r="T13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr">
+      <c r="U13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="20"/>
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="20"/>
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="20"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="20"/>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="20"/>
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="O14" s="20"/>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="S14" s="20"/>
+      <c r="T14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
+      <c r="U14" s="20"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">야월삼경</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="17"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="21"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="21"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="21"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="21"/>
+      <c r="T17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="U17" s="18"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="17"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U18" s="19"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="17"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U19" s="20"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="17"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="U20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="17"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U21" s="19"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="17"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="U22" s="20"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="17"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="21"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="21"/>
+      <c r="T23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U23" s="18"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="17"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="17"/>
+      <c r="S24" s="22"/>
+      <c r="T24" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U24" s="19"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="17"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="17"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U25" s="20"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="17"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="17"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U26" s="18"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="17"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="17"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+㳞</t>
+        </is>
+      </c>
+      <c r="U27" s="19"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="17"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="17"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="17"/>
+      <c r="S28" s="23"/>
+      <c r="T28" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="U28" s="20"/>
     </row>
   </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야월삼경 — 민요채보-2/야월삼경.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-姑</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-㳞</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-    </row>
-  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -631,12 +631,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2"/>
@@ -947,12 +947,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞</t>
+          <t xml:space="preserve">–|㳞</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -1847,12 +1847,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -1963,12 +1963,12 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -2657,12 +2657,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2766,12 +2766,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -2916,12 +2916,12 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無|潢</t>
+          <t xml:space="preserve">–|無|潢</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 潢</t>
         </is>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㴌</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -3719,12 +3719,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -3833,12 +3833,12 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|無</t>
+          <t xml:space="preserve">–|無</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4091,12 +4091,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|·</t>
+          <t xml:space="preserve">–|·</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
@@ -4246,7 +4246,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4280,7 +4280,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無
 潢</t>
         </is>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4376,13 +4376,13 @@
       <c r="M5" s="10"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q5" s="10"/>
@@ -4475,7 +4475,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4508,7 +4508,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4517,7 +4517,7 @@
       <c r="M7" s="9"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4621,7 +4621,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 無</t>
         </is>
       </c>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="9"/>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="L10" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
@@ -4949,7 +4949,7 @@
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4958,7 +4958,7 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4971,7 +4971,7 @@
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
@@ -4984,7 +4984,7 @@
       <c r="O13" s="9"/>
       <c r="P13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4994,7 +4994,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ·</t>
         </is>
       </c>

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4136,107 +4177,107 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">야월삼경</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4244,73 +4285,73 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="23"/>
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="23"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N4" s="18" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="12" t="inlineStr">
+      <c r="O4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P4" s="17" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="Q4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4318,154 +4359,154 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無
 潢</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 潕</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="M5" s="26"/>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="10"/>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="O5" s="26"/>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="10"/>
+      <c r="Q5" s="26"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="G6" s="8"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4473,145 +4514,145 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="C7" s="23"/>
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 潢</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="23"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="23"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="K7" s="23"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="O7" s="23"/>
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q7" s="9"/>
+      <c r="Q7" s="23"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潕
 㴌</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="26"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潕</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P8" s="18" t="inlineStr">
+      <c r="P8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 潢
 潕</t>
         </is>
       </c>
-      <c r="Q8" s="13" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -4619,83 +4660,83 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
@@ -4703,75 +4744,75 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="23"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="L10" s="18" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="N10" s="18" t="inlineStr">
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">맞</t>
         </is>
       </c>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="Q10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
@@ -4779,78 +4820,78 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="26"/>
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="L11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M11" s="13" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="O11" s="10" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="Q11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -4858,82 +4899,82 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
+      <c r="N12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P12" s="17" t="inlineStr">
+      <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -4941,108 +4982,108 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="23"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="23"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ·</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="26"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ·</t>
         </is>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="K14" s="26"/>
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌
 ○</t>
         </is>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="17" t="inlineStr">
+      <c r="M14" s="27"/>
+      <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ·</t>
         </is>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="O14" s="26"/>
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -4154,28 +4154,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="26"/>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="Q5" s="26"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4753,13 +4753,13 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4830,13 +4830,13 @@
       <c r="C11" s="26"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="26" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="26"/>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -4980,11 +4980,11 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="23"/>
@@ -5006,7 +5006,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-·</t>
+–</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -5058,8 +5058,8 @@
       <c r="I14" s="26"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-·</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="K14" s="26"/>
@@ -5073,8 +5073,8 @@
       <c r="M14" s="27"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-·</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="O14" s="26"/>

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -1924,14 +1924,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㴌|○</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㴌
-○</t>
+㴌</t>
         </is>
       </c>
       <c r="I36" s="3"/>
@@ -5066,8 +5065,7 @@
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㴌
-○</t>
+㴌</t>
         </is>
       </c>
       <c r="M14" s="27"/>

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4204,7 +4227,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
@@ -4214,7 +4237,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
@@ -4224,7 +4247,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4235,7 +4258,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4245,7 +4268,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
@@ -4256,7 +4279,7 @@
 汰</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
@@ -4266,7 +4289,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4276,7 +4299,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4290,13 +4313,13 @@
 仲</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
@@ -4306,7 +4329,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4317,20 +4340,20 @@
 汰</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
+      <c r="I4" s="30"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="30"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -4340,7 +4363,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O4" s="25" t="inlineStr">
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4350,7 +4373,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="Q4" s="23" t="inlineStr">
+      <c r="Q4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -4363,7 +4386,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4375,7 +4398,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">흘</t>
         </is>
@@ -4386,14 +4409,14 @@
 無</t>
         </is>
       </c>
-      <c r="G5" s="26"/>
+      <c r="G5" s="32"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 潕</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4403,7 +4426,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4413,19 +4436,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="26"/>
+      <c r="M5" s="32"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="26"/>
+      <c r="O5" s="32"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="26"/>
+      <c r="Q5" s="32"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -4434,7 +4457,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -4444,7 +4467,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4455,14 +4478,14 @@
 潢</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="29"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4473,7 +4496,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4483,7 +4506,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -4494,7 +4517,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4505,7 +4528,7 @@
 潢</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
@@ -4519,14 +4542,14 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="23"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 潢</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
@@ -4537,7 +4560,7 @@
 南</t>
         </is>
       </c>
-      <c r="G7" s="23"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
@@ -4545,30 +4568,30 @@
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="23"/>
+      <c r="I7" s="30"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="23"/>
+      <c r="M7" s="30"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="O7" s="23"/>
+      <c r="O7" s="30"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q7" s="23"/>
+      <c r="Q7" s="30"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -4577,7 +4600,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4589,7 +4612,7 @@
 㴌</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
@@ -4601,14 +4624,14 @@
 仲</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="26" t="inlineStr">
+      <c r="I8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
@@ -4618,7 +4641,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">시</t>
         </is>
@@ -4628,7 +4651,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -4639,7 +4662,7 @@
 潕</t>
         </is>
       </c>
-      <c r="O8" s="26" t="inlineStr">
+      <c r="O8" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4651,7 +4674,7 @@
 潕</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -4665,13 +4688,13 @@
 無</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4681,7 +4704,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -4692,7 +4715,7 @@
 汰</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4703,7 +4726,7 @@
 潢</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
@@ -4713,7 +4736,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4724,7 +4747,7 @@
 潢</t>
         </is>
       </c>
-      <c r="O9" s="28" t="inlineStr">
+      <c r="O9" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
@@ -4735,7 +4758,7 @@
 汰</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
@@ -4749,19 +4772,19 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="23"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4771,14 +4794,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
@@ -4789,7 +4812,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="M10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
@@ -4800,7 +4823,7 @@
 南</t>
         </is>
       </c>
-      <c r="O10" s="25" t="inlineStr">
+      <c r="O10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">맞</t>
         </is>
@@ -4811,7 +4834,7 @@
 南</t>
         </is>
       </c>
-      <c r="Q10" s="23" t="inlineStr">
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
@@ -4826,19 +4849,19 @@
 仲</t>
         </is>
       </c>
-      <c r="C11" s="26"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4848,7 +4871,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="26"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -4856,7 +4879,7 @@
 仲</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4866,7 +4889,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="M11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4878,7 +4901,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O11" s="26" t="inlineStr">
+      <c r="O11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4890,7 +4913,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="26" t="inlineStr">
+      <c r="Q11" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -4903,7 +4926,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4913,7 +4936,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4923,7 +4946,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4933,7 +4956,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4943,7 +4966,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
@@ -4953,7 +4976,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -4963,7 +4986,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="22" t="inlineStr">
+      <c r="O12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4973,7 +4996,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q12" s="22" t="inlineStr">
+      <c r="Q12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
@@ -4986,49 +5009,49 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="30"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="23"/>
+      <c r="G13" s="30"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="30"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="30"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="30"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O13" s="23"/>
+      <c r="O13" s="30"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="Q13" s="23"/>
+      <c r="Q13" s="30"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -5038,50 +5061,50 @@
 –</t>
         </is>
       </c>
-      <c r="C14" s="26"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E14" s="26"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="26"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="K14" s="26"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="O14" s="26"/>
+      <c r="O14" s="32"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="26"/>
+      <c r="Q14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -223,10 +218,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
@@ -236,27 +234,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -357,7 +334,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">93</t>
+          <t xml:space="preserve">95</t>
         </is>
       </c>
     </row>
@@ -369,7 +346,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -429,7 +406,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 상단 "야월삼경 &lt;중모리&gt; C#키". 12정간, 굵은 선 3칸마다, 8줄 사용(오른쪽 2칸은 빈 양식 칸). 가사는 "야월삼경 달밝은데 …"로 이어짐. 청성(氵) 반복 가락 많음. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 오른쪽 상단 "야월삼경 &lt;중모리&gt; C#키". 12정간, 굵은 선 3칸마다 → 3/4. 오른쪽 맨 끝 빈 칸 제외, 오른쪽부터 8줄 사용(왼쪽 2칸 빈 줄). 가사는 각 율명 줄 오른쪽 칸. 정간 안 짧은 가로선·작은 사선 점은 모두 – 로 적음. 줄3·줄5 등 청성(㴌·㳞·湳) 가락 반복. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -617,17 +594,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J2" s="4"/>
@@ -656,12 +633,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -730,13 +707,13 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|潢</t>
+          <t xml:space="preserve">㳞|湳</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-潢</t>
+湳</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -804,28 +781,23 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|潢|潕</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢
-潕</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|無</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">셋째 글자 潕 확실치 않음</t>
-        </is>
-      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -851,13 +823,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰</t>
+          <t xml:space="preserve">南|潢</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
+          <t xml:space="preserve">南
+潢</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1121,12 +1093,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南^</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1136,7 +1108,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽에 작은 사선</t>
+          <t xml:space="preserve">南 오른쪽 작은 꺾쇠</t>
         </is>
       </c>
       <c r="K15" s="2"/>
@@ -1197,23 +1169,27 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|仲</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌仲|–</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌仲
+–</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="J17" s="4"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌仲 나란히</t>
+        </is>
+      </c>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1275,13 +1251,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潕</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潕</t>
+無</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1313,27 +1289,23 @@
       <c r="F20" s="2">
         <v>3</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南|潢</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밝</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 밝/걸?</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
+        </is>
+      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
     <row r="21">
@@ -1370,12 +1342,12 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">맞</t>
+          <t xml:space="preserve">간</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">가사 맞/깟?</t>
+          <t xml:space="preserve">가사 간/갓?</t>
         </is>
       </c>
       <c r="K21" s="2"/>
@@ -1444,12 +1416,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1481,18 +1453,22 @@
       <c r="F24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 오른쪽 작은 꺾쇠</t>
+        </is>
+      </c>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1518,13 +1494,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1554,18 +1530,18 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㴌|–湳</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㴌
+–湳</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">밝</t>
+          <t xml:space="preserve">밤</t>
         </is>
       </c>
       <c r="J26" s="4"/>
@@ -1631,18 +1607,22 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 사선, · 일 수도</t>
+        </is>
+      </c>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1746,12 +1726,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1783,27 +1763,23 @@
       <c r="F32" s="2">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|㳞</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|湳</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
+湳</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 새/세?</t>
-        </is>
-      </c>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
     </row>
     <row r="33">
@@ -1827,26 +1803,22 @@
       <c r="F33" s="2">
         <v>3</v>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 는/노?</t>
-        </is>
-      </c>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
     </row>
     <row r="34">
@@ -1872,12 +1844,12 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1911,13 +1883,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|㴌</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
+湳</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1945,23 +1917,20 @@
       <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞|㴌</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞|㴌|△</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="I36" s="3"/>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맨 아래 ○</t>
-        </is>
-      </c>
+㴌
+△</t>
+        </is>
+      </c>
+      <c r="I36" s="2"/>
+      <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -2099,23 +2068,27 @@
       <c r="F40" s="2">
         <v>2</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|潢</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢|–</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+–</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="J40" s="4"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢 둘레에 점선 네모(수정 표시?)</t>
+        </is>
+      </c>
       <c r="K40" s="2"/>
     </row>
     <row r="41">
@@ -2187,7 +2160,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">시</t>
+          <t xml:space="preserve">식</t>
         </is>
       </c>
       <c r="J42" s="4"/>
@@ -2376,12 +2349,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2411,13 +2384,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2447,13 +2420,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -2487,16 +2459,20 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I50" s="2"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
@@ -2523,18 +2499,18 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|潕</t>
+          <t xml:space="preserve">潢|無</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-潕</t>
+          <t xml:space="preserve">潢
+無</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">우</t>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2563,18 +2539,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화</t>
+          <t xml:space="preserve">성</t>
         </is>
       </c>
       <c r="J52" s="4"/>
@@ -2603,17 +2578,20 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰|㴌</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰
 㴌</t>
         </is>
       </c>
-      <c r="I53" s="2"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화로</t>
+        </is>
+      </c>
       <c r="J53" s="4"/>
       <c r="K53" s="2"/>
     </row>
@@ -2640,18 +2618,18 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|㳞</t>
+          <t xml:space="preserve">湳|㳞</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">湳
 㳞</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">성</t>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J54" s="4"/>
@@ -2680,18 +2658,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J55" s="4"/>
@@ -2755,12 +2732,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2829,13 +2806,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|㴌</t>
+          <t xml:space="preserve">–|湳</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
+湳</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2899,22 +2876,26 @@
       <c r="F61" s="2">
         <v>1</v>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="J61" s="4"/>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 삼/산?</t>
+        </is>
+      </c>
       <c r="K61" s="2"/>
     </row>
     <row r="62">
@@ -3024,7 +3005,11 @@
 潢</t>
         </is>
       </c>
-      <c r="I64" s="2"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -3060,7 +3045,11 @@
 南</t>
         </is>
       </c>
-      <c r="I65" s="2"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -3097,7 +3086,11 @@
 仲</t>
         </is>
       </c>
-      <c r="I66" s="2"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -3134,7 +3127,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">돈</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J67" s="4"/>
@@ -3163,19 +3156,16 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I68" s="2"/>
       <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
@@ -3202,19 +3192,15 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
-        </is>
-      </c>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I69" s="2"/>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3241,12 +3227,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3267,32 +3253,28 @@
         </is>
       </c>
       <c r="C71" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D71" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">찬</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I71" s="2"/>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
     </row>
@@ -3306,32 +3288,28 @@
         </is>
       </c>
       <c r="C72" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D72" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E72" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">길</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I72" s="2"/>
       <c r="J72" s="4"/>
       <c r="K72" s="2"/>
     </row>
@@ -3351,112 +3329,111 @@
         <v>7</v>
       </c>
       <c r="E73" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73" s="2">
         <v>1</v>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">찬</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 찬/차?</t>
+        </is>
+      </c>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C74" s="2">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2">
+        <v>7</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">길</t>
+        </is>
+      </c>
+      <c r="J74" s="4"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C75" s="2">
+        <v>7</v>
+      </c>
+      <c r="D75" s="2">
+        <v>7</v>
+      </c>
+      <c r="E75" s="2">
+        <v>3</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–|無|潢</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無
 潢</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흘</t>
-        </is>
-      </c>
-      <c r="J73" s="4"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>1</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C74" s="2">
-        <v>7</v>
-      </c>
-      <c r="D74" s="2">
-        <v>7</v>
-      </c>
-      <c r="E74" s="2">
-        <v>4</v>
-      </c>
-      <c r="F74" s="2">
-        <v>2</v>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J74" s="4"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>1</v>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C75" s="2">
-        <v>7</v>
-      </c>
-      <c r="D75" s="2">
-        <v>7</v>
-      </c>
-      <c r="E75" s="2">
-        <v>5</v>
-      </c>
-      <c r="F75" s="2">
-        <v>2</v>
-      </c>
-      <c r="G75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌|潢</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-潢</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">찬</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 찬/긴?</t>
-        </is>
-      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
     <row r="76">
@@ -3475,26 +3452,24 @@
         <v>7</v>
       </c>
       <c r="E76" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F76" s="2">
         <v>2</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潕|㴌</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潕
-㴌</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">밤</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J76" s="4"/>
@@ -3516,24 +3491,25 @@
         <v>7</v>
       </c>
       <c r="E77" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F77" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㳞
+㴌</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">긴</t>
         </is>
       </c>
       <c r="J77" s="4"/>
@@ -3555,22 +3531,28 @@
         <v>7</v>
       </c>
       <c r="E78" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F78" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">潢|無|潢</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
+          <t xml:space="preserve">潢
+無
+潢</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밤</t>
+        </is>
+      </c>
       <c r="J78" s="4"/>
       <c r="K78" s="2"/>
     </row>
@@ -3590,22 +3572,26 @@
         <v>7</v>
       </c>
       <c r="E79" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F79" s="2">
         <v>3</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="J79" s="4"/>
       <c r="K79" s="2"/>
     </row>
@@ -3625,26 +3611,22 @@
         <v>7</v>
       </c>
       <c r="E80" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I80" s="2"/>
       <c r="J80" s="4"/>
       <c r="K80" s="2"/>
     </row>
@@ -3664,20 +3646,19 @@
         <v>7</v>
       </c>
       <c r="E81" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|㴌</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-㴌</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3700,95 +3681,95 @@
         <v>7</v>
       </c>
       <c r="E82" s="2">
+        <v>10</v>
+      </c>
+      <c r="F82" s="2">
+        <v>4</v>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음</t>
+        </is>
+      </c>
+      <c r="J82" s="4"/>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2">
+        <v>1</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C83" s="2">
+        <v>7</v>
+      </c>
+      <c r="D83" s="2">
+        <v>7</v>
+      </c>
+      <c r="E83" s="2">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2">
+        <v>4</v>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|湳</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+湳</t>
+        </is>
+      </c>
+      <c r="I83" s="2"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2">
+        <v>1</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C84" s="2">
+        <v>7</v>
+      </c>
+      <c r="D84" s="2">
+        <v>7</v>
+      </c>
+      <c r="E84" s="2">
         <v>12</v>
       </c>
-      <c r="F82" s="2">
-        <v>4</v>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="F84" s="2">
+        <v>4</v>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞|㴌</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
-        </is>
-      </c>
-      <c r="I82" s="2"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2">
-        <v>1</v>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C83" s="2">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2">
-        <v>8</v>
-      </c>
-      <c r="E83" s="2">
-        <v>1</v>
-      </c>
-      <c r="F83" s="2">
-        <v>1</v>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">큰</t>
-        </is>
-      </c>
-      <c r="J83" s="4"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>1</v>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C84" s="2">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2">
-        <v>8</v>
-      </c>
-      <c r="E84" s="2">
-        <v>2</v>
-      </c>
-      <c r="F84" s="2">
-        <v>1</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|仲</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3811,24 +3792,24 @@
         <v>8</v>
       </c>
       <c r="E85" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F85" s="2">
         <v>1</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">큰</t>
         </is>
       </c>
       <c r="J85" s="4"/>
@@ -3850,26 +3831,23 @@
         <v>8</v>
       </c>
       <c r="E86" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F86" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+仲</t>
+        </is>
+      </c>
+      <c r="I86" s="2"/>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3889,20 +3867,19 @@
         <v>8</v>
       </c>
       <c r="E87" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F87" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I87" s="2"/>
@@ -3925,27 +3902,31 @@
         <v>8</v>
       </c>
       <c r="E88" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F88" s="2">
         <v>2</v>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="J88" s="4"/>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢 오른쪽 작은 ㄱ 꺾쇠</t>
+        </is>
+      </c>
       <c r="K88" s="2"/>
     </row>
     <row r="89">
@@ -3964,10 +3945,10 @@
         <v>8</v>
       </c>
       <c r="E89" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F89" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -4000,133 +3981,138 @@
         <v>8</v>
       </c>
       <c r="E90" s="2">
+        <v>6</v>
+      </c>
+      <c r="F90" s="2">
+        <v>2</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
+        </is>
+      </c>
+      <c r="J90" s="4"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2">
+        <v>1</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C91" s="2">
         <v>8</v>
       </c>
-      <c r="F90" s="2">
-        <v>3</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="D91" s="2">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2">
+        <v>7</v>
+      </c>
+      <c r="F91" s="2">
+        <v>3</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無|潢</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로</t>
+        </is>
+      </c>
+      <c r="J91" s="4"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2">
+        <v>1</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C92" s="2">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2">
+        <v>8</v>
+      </c>
+      <c r="E92" s="2">
+        <v>8</v>
+      </c>
+      <c r="F92" s="2">
+        <v>3</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無|南</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>1</v>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C91" s="2">
+      <c r="I92" s="2"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2">
+        <v>1</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C93" s="2">
         <v>8</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D93" s="2">
         <v>8</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E93" s="2">
         <v>9</v>
       </c>
-      <c r="F91" s="2">
-        <v>3</v>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F93" s="2">
+        <v>3</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲|姑|仲</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑
 仲</t>
         </is>
       </c>
-      <c r="I91" s="2"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>1</v>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C92" s="2">
-        <v>8</v>
-      </c>
-      <c r="D92" s="2">
-        <v>8</v>
-      </c>
-      <c r="E92" s="2">
-        <v>10</v>
-      </c>
-      <c r="F92" s="2">
-        <v>4</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="J92" s="4"/>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>1</v>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
-        </is>
-      </c>
-      <c r="C93" s="2">
-        <v>8</v>
-      </c>
-      <c r="D93" s="2">
-        <v>8</v>
-      </c>
-      <c r="E93" s="2">
-        <v>11</v>
-      </c>
-      <c r="F93" s="2">
-        <v>4</v>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
       <c r="I93" s="2"/>
       <c r="J93" s="4"/>
       <c r="K93" s="2"/>
@@ -4147,28 +4133,102 @@
         <v>8</v>
       </c>
       <c r="E94" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2">
         <v>4</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-·</t>
-        </is>
-      </c>
-      <c r="I94" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J94" s="4"/>
       <c r="K94" s="2"/>
     </row>
+    <row r="95">
+      <c r="A95" s="2">
+        <v>1</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C95" s="2">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2">
+        <v>11</v>
+      </c>
+      <c r="F95" s="2">
+        <v>4</v>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I95" s="2"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2">
+        <v>1</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-2/야월삼경.png</t>
+        </is>
+      </c>
+      <c r="C96" s="2">
+        <v>8</v>
+      </c>
+      <c r="D96" s="2">
+        <v>8</v>
+      </c>
+      <c r="E96" s="2">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2">
+        <v>4</v>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I96" s="2"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K94"/>
+  <autoFilter ref="A1:K96"/>
 </worksheet>
 </file>
 
@@ -4197,7 +4257,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4220,45 +4280,44 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">찬</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4268,20 +4327,20 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="M3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밝</t>
+          <t xml:space="preserve">㴌
+–湳</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밤</t>
         </is>
       </c>
       <c r="N3" s="21" t="inlineStr">
@@ -4289,23 +4348,23 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="O3" s="29" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="Q3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="82.06" customHeight="1">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="77.61" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4313,13 +4372,13 @@
 仲</t>
         </is>
       </c>
-      <c r="C4" s="30"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">길</t>
         </is>
@@ -4329,7 +4388,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="30" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4337,60 +4396,60 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I4" s="30"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="K4" s="30"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M4" s="30" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="N4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O4" s="31" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="O4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="Q4" s="30" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="82.06" customHeight="1">
+    <row r="5" ht="77.61" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
+      <c r="C5" s="27"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
@@ -4398,9 +4457,9 @@
 潢</t>
         </is>
       </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">흘</t>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -4409,16 +4468,16 @@
 無</t>
         </is>
       </c>
-      <c r="G5" s="32"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-潕</t>
-        </is>
-      </c>
-      <c r="I5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="I5" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4426,48 +4485,48 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="32" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="32"/>
+      <c r="M5" s="28"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O5" s="32"/>
+      <c r="O5" s="27"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q5" s="32"/>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
+      <c r="Q5" s="27"/>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢^</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">성</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4478,63 +4537,66 @@
 潢</t>
         </is>
       </c>
-      <c r="G6" s="29"/>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">성</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無潢
+–</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">소</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">적</t>
+        </is>
+      </c>
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌仲
+–</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">소</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">적</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-仲</t>
-        </is>
-      </c>
-      <c r="O6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="P6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="29" t="inlineStr">
+湳</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="82.06" customHeight="1">
+    <row r="7" ht="77.61" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4542,16 +4604,16 @@
 無</t>
         </is>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-潢</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">찬</t>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">긴</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -4560,47 +4622,55 @@
 南</t>
         </is>
       </c>
-      <c r="G7" s="30"/>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
+        </is>
+      </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-汰
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="30"/>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화
+로</t>
+        </is>
+      </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 無</t>
         </is>
       </c>
-      <c r="K7" s="30"/>
+      <c r="K7" s="25"/>
       <c r="L7" s="21"/>
-      <c r="M7" s="30"/>
+      <c r="M7" s="25"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㴌</t>
         </is>
       </c>
-      <c r="O7" s="30"/>
+      <c r="O7" s="25"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="Q7" s="30"/>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4608,11 +4678,11 @@
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潕
-㴌</t>
-        </is>
-      </c>
-      <c r="E8" s="32" t="inlineStr">
+無
+潢</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
@@ -4624,16 +4694,20 @@
 仲</t>
         </is>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">우</t>
+        </is>
+      </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
+          <t xml:space="preserve">湳
 㳞</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">성</t>
+      <c r="I8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">구</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -4641,9 +4715,9 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">시</t>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">식</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -4651,7 +4725,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M8" s="32" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">적</t>
         </is>
@@ -4659,112 +4733,114 @@
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潕</t>
-        </is>
-      </c>
-      <c r="O8" s="32" t="inlineStr">
+無</t>
+        </is>
+      </c>
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="P8" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-潢
-潕</t>
-        </is>
-      </c>
-      <c r="Q8" s="33" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+無</t>
+        </is>
+      </c>
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="82.06" customHeight="1">
+    <row r="9" ht="77.61" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-無</t>
-        </is>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">돈</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-汰</t>
-        </is>
-      </c>
-      <c r="I9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">로</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+潢</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">돈</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="N9" s="24" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="O9" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">밝</t>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">별</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-汰</t>
-        </is>
-      </c>
-      <c r="Q9" s="29" t="inlineStr">
+          <t xml:space="preserve">南
+潢</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="82.06" customHeight="1">
+    <row r="10" ht="77.61" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4772,60 +4848,57 @@
 南</t>
         </is>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I10" s="30"/>
+      <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="K10" s="30" t="inlineStr">
+      <c r="K10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">절</t>
         </is>
       </c>
-      <c r="L10" s="24" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㳞</t>
-        </is>
-      </c>
-      <c r="M10" s="31" t="inlineStr">
+湳</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">새</t>
         </is>
       </c>
-      <c r="N10" s="24" t="inlineStr">
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">맞</t>
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -4834,13 +4907,13 @@
 南</t>
         </is>
       </c>
-      <c r="Q10" s="30" t="inlineStr">
+      <c r="Q10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">밝</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="82.06" customHeight="1">
+    <row r="11" ht="77.61" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4849,29 +4922,25 @@
 仲</t>
         </is>
       </c>
-      <c r="C11" s="32"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="27"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I11" s="32"/>
+      <c r="I11" s="27"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
@@ -4879,17 +4948,17 @@
 仲</t>
         </is>
       </c>
-      <c r="K11" s="32" t="inlineStr">
+      <c r="K11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L11" s="24" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M11" s="33" t="inlineStr">
+      <c r="M11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4901,7 +4970,7 @@
 仲</t>
         </is>
       </c>
-      <c r="O11" s="32" t="inlineStr">
+      <c r="O11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4913,20 +4982,20 @@
 仲</t>
         </is>
       </c>
-      <c r="Q11" s="32" t="inlineStr">
+      <c r="Q11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="77.61" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4936,17 +5005,17 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G12" s="29" t="inlineStr">
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4956,7 +5025,7 @@
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I12" s="29" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4966,145 +5035,154 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K12" s="29" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">네</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="P12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="29" t="inlineStr">
+      <c r="Q12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="77.61" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
-        </is>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="30"/>
+湳</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
-        </is>
-      </c>
-      <c r="I13" s="30"/>
+湳</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="30"/>
+      <c r="K13" s="25"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌</t>
-        </is>
-      </c>
-      <c r="M13" s="30"/>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="O13" s="30"/>
+湳</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南^</t>
+        </is>
+      </c>
+      <c r="O13" s="26"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="Q13" s="30"/>
-    </row>
-    <row r="14" ht="82.06" customHeight="1">
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="27"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="32"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G14" s="27"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㴌</t>
         </is>
       </c>
-      <c r="I14" s="32"/>
+      <c r="I14" s="27"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="24" t="inlineStr">
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-㴌</t>
-        </is>
-      </c>
-      <c r="M14" s="33"/>
+㴌
+△</t>
+        </is>
+      </c>
+      <c r="M14" s="27"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="O14" s="32"/>
+△</t>
+        </is>
+      </c>
+      <c r="O14" s="27"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="32"/>
+      <c r="Q14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -563,10 +563,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -509,17 +509,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -636,7 +636,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -694,6 +694,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4051,576 +4095,576 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="22"/>
+      <c r="D4" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="22"/>
+      <c r="L4" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="7" t="s">
+      <c r="M5" s="25"/>
+      <c r="N5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="7" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="9" t="s">
+      <c r="Q5" s="24"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B6" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="N6" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="10" t="s">
+      <c r="O6" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="19" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="22"/>
+      <c r="D7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="7" t="s">
+      <c r="K7" s="22"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="O7" s="11"/>
-      <c r="P7" s="7" t="s">
+      <c r="O7" s="22"/>
+      <c r="P7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q7" s="11"/>
-    </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="Q7" s="22"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="K8" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="13" t="s">
+      <c r="Q8" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="22"/>
+      <c r="D10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="Q10" s="22" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="7" t="s">
+      <c r="C11" s="24"/>
+      <c r="D11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="24"/>
+      <c r="F11" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11" s="24"/>
+      <c r="H11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="7" t="s">
+      <c r="I11" s="24"/>
+      <c r="J11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="O11" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="Q11" s="13" t="s">
+      <c r="Q11" s="24" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="9" t="s">
+      <c r="M13" s="22"/>
+      <c r="N13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="O13" s="12"/>
-      <c r="P13" s="7" t="s">
+      <c r="O13" s="23"/>
+      <c r="P13" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="24"/>
+      <c r="F14" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="7" t="s">
+      <c r="I14" s="24"/>
+      <c r="J14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="24"/>
+      <c r="L14" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="7" t="s">
+      <c r="M14" s="24"/>
+      <c r="N14" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="7" t="s">
+      <c r="O14" s="24"/>
+      <c r="P14" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q14" s="13"/>
+      <c r="Q14" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4628,7 +4672,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/야월삼경.xlsx
+++ b/sheets/민요/검수/야월삼경.xlsx
@@ -4101,26 +4101,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4140,7 +4140,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>68</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>71</v>
       </c>
@@ -4236,7 +4236,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>72</v>
       </c>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B6" s="20" t="s">
         <v>141</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>108</v>
       </c>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Q7" s="22"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>72</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>111</v>
       </c>
@@ -4464,7 +4464,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>63</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>66</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>72</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>50</v>
       </c>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="Q13" s="22"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>88</v>
       </c>
@@ -4672,7 +4672,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
